--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N68_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>5.026097686941926</v>
       </c>
       <c r="E2" t="n">
-        <v>5.977218731160892</v>
+        <v>5.242949939970035</v>
       </c>
       <c r="F2" t="n">
-        <v>7.931831438159782</v>
+        <v>6.870833903241444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>23.65896956471136</v>
       </c>
       <c r="E3" t="n">
-        <v>5.977218731160892</v>
+        <v>5.242949939970035</v>
       </c>
       <c r="F3" t="n">
-        <v>7.931831438159782</v>
+        <v>6.870833903241444</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>19.1095913163923</v>
       </c>
       <c r="E4" t="n">
-        <v>5.977218731160892</v>
+        <v>5.242949939970035</v>
       </c>
       <c r="F4" t="n">
-        <v>7.931831438159782</v>
+        <v>6.870833903241444</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -561,6 +561,38 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N68.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11.53582935649019</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.58210717384879</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.242949939970035</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.870833903241444</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.169775053943153</v>
+        <v>0.8400884462657623</v>
       </c>
       <c r="D2" t="n">
-        <v>5.026097686941926</v>
+        <v>0.816740874128063</v>
       </c>
       <c r="E2" t="n">
-        <v>5.242949939970035</v>
+        <v>0.8519793652451305</v>
       </c>
       <c r="F2" t="n">
-        <v>6.870833903241444</v>
+        <v>1.116510509276734</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.06239186818844</v>
+        <v>2.935138678580622</v>
       </c>
       <c r="D3" t="n">
-        <v>23.65896956471136</v>
+        <v>3.844582554265596</v>
       </c>
       <c r="E3" t="n">
-        <v>5.242949939970035</v>
+        <v>0.8519793652451305</v>
       </c>
       <c r="F3" t="n">
-        <v>6.870833903241444</v>
+        <v>1.116510509276734</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.607134244987122</v>
+        <v>0.9111593148104072</v>
       </c>
       <c r="D4" t="n">
-        <v>19.1095913163923</v>
+        <v>3.105308588913749</v>
       </c>
       <c r="E4" t="n">
-        <v>5.242949939970035</v>
+        <v>0.8519793652451305</v>
       </c>
       <c r="F4" t="n">
-        <v>6.870833903241444</v>
+        <v>1.116510509276734</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.53582935649019</v>
+        <v>1.874572270429656</v>
       </c>
       <c r="D5" t="n">
-        <v>15.58210717384879</v>
+        <v>2.532092415750428</v>
       </c>
       <c r="E5" t="n">
-        <v>5.242949939970035</v>
+        <v>0.8519793652451305</v>
       </c>
       <c r="F5" t="n">
-        <v>6.870833903241444</v>
+        <v>1.116510509276734</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
